--- a/artfynd/A 40880-2024 artfynd.xlsx
+++ b/artfynd/A 40880-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150840</v>
+        <v>121150839</v>
       </c>
       <c r="B2" t="n">
-        <v>91957</v>
+        <v>91965</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>845005</v>
+        <v>844988</v>
       </c>
       <c r="R2" t="n">
-        <v>7531416</v>
+        <v>7531054</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150839</v>
+        <v>121150840</v>
       </c>
       <c r="B3" t="n">
-        <v>91955</v>
+        <v>91967</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>844988</v>
+        <v>845005</v>
       </c>
       <c r="R3" t="n">
-        <v>7531054</v>
+        <v>7531416</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 40880-2024 artfynd.xlsx
+++ b/artfynd/A 40880-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150839</v>
+        <v>121150840</v>
       </c>
       <c r="B2" t="n">
-        <v>91965</v>
+        <v>91967</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>844988</v>
+        <v>845005</v>
       </c>
       <c r="R2" t="n">
-        <v>7531054</v>
+        <v>7531416</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150840</v>
+        <v>121150839</v>
       </c>
       <c r="B3" t="n">
-        <v>91967</v>
+        <v>91965</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>845005</v>
+        <v>844988</v>
       </c>
       <c r="R3" t="n">
-        <v>7531416</v>
+        <v>7531054</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 40880-2024 artfynd.xlsx
+++ b/artfynd/A 40880-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121150840</v>
       </c>
       <c r="B2" t="n">
-        <v>91967</v>
+        <v>91979</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>121150839</v>
       </c>
       <c r="B3" t="n">
-        <v>91965</v>
+        <v>91977</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 40880-2024 artfynd.xlsx
+++ b/artfynd/A 40880-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150840</v>
+        <v>121150839</v>
       </c>
       <c r="B2" t="n">
-        <v>91979</v>
+        <v>91978</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>845005</v>
+        <v>844988</v>
       </c>
       <c r="R2" t="n">
-        <v>7531416</v>
+        <v>7531054</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150839</v>
+        <v>121150840</v>
       </c>
       <c r="B3" t="n">
-        <v>91977</v>
+        <v>91980</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>844988</v>
+        <v>845005</v>
       </c>
       <c r="R3" t="n">
-        <v>7531054</v>
+        <v>7531416</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 40880-2024 artfynd.xlsx
+++ b/artfynd/A 40880-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121150839</v>
       </c>
       <c r="B2" t="n">
-        <v>91978</v>
+        <v>91981</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>121150840</v>
       </c>
       <c r="B3" t="n">
-        <v>91980</v>
+        <v>91983</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 40880-2024 artfynd.xlsx
+++ b/artfynd/A 40880-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150839</v>
+        <v>121150840</v>
       </c>
       <c r="B2" t="n">
-        <v>91981</v>
+        <v>91983</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>844988</v>
+        <v>845005</v>
       </c>
       <c r="R2" t="n">
-        <v>7531054</v>
+        <v>7531416</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150840</v>
+        <v>121150839</v>
       </c>
       <c r="B3" t="n">
-        <v>91983</v>
+        <v>91981</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>845005</v>
+        <v>844988</v>
       </c>
       <c r="R3" t="n">
-        <v>7531416</v>
+        <v>7531054</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
